--- a/tools/missing-not-in-prompts-with-prompts.xlsx
+++ b/tools/missing-not-in-prompts-with-prompts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,12 +431,3996 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>burrito</t>
+          <t>basalisk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>clean vector clipart of burrito, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+          <t>clean vector clipart of basalisk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>blame</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>clean vector clipart of blame, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>clean vector clipart of blank, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>blur</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>clean vector clipart of blur, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bombproof</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>clean vector clipart of bombproof, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>booster</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>clean vector clipart of booster, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>clean vector clipart of bracelet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>brisk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>clean vector clipart of brisk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>broccoli</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>clean vector clipart of broccoli, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bronze</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>clean vector clipart of bronze, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>clean vector clipart of brown, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bugler</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>clean vector clipart of bugler, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bust</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>clean vector clipart of bust, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>clean vector clipart of butterfly, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>camoflauge</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>clean vector clipart of camoflauge, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>capriole</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>clean vector clipart of capriole, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>capris</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>clean vector clipart of capris, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>capsule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>clean vector clipart of capsule, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>carefree</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>clean vector clipart of carefree, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cask</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cask, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cast, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cauliflower</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cauliflower, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>chakra</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>clean vector clipart of chakra, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>chaplain</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>clean vector clipart of chaplain, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>clean vector clipart of Christmas, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>circlet</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>clean vector clipart of circlet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>clarinet</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>clean vector clipart of clarinet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>clasp</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>clean vector clipart of clasp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>clean vector clipart of clean, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cleat</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cleat, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>clean vector clipart of clip, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cloak</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cloak, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cobbler</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cobbler, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>coleslaw</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>clean vector clipart of coleslaw, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>clean vector clipart of complete, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>compress</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>clean vector clipart of compress, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cornflakes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cornflakes, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cosmic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cosmic, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>costume</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>clean vector clipart of costume, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>counsel</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>clean vector clipart of counsel, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>crack</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crack, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cradle</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cradle, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>creepy</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>clean vector clipart of creepy, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>crepe</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crepe, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>crisp</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crisp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>crispy</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crispy, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>criticism</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>clean vector clipart of criticism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>crown</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crown, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>crust</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crust, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>crystal</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>clean vector clipart of crystal, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cyclone</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cyclone, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cyclops</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>clean vector clipart of cyclops, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>debris</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>clean vector clipart of debris, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>declare</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>clean vector clipart of declare, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>deflate</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>clean vector clipart of deflate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>clean vector clipart of degree, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>clean vector clipart of degrees, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>deplete</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>clean vector clipart of deplete, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>dewclaw</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dewclaw, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>diffraction</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>clean vector clipart of diffraction, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>clean vector clipart of disc, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disco</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>clean vector clipart of disco, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>discover</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>clean vector clipart of discover, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>dislocate</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dislocate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>clean vector clipart of display, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>dog sled</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dog sled, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>dragonfly</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dragonfly, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>drain</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drain, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>drama</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drama, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>drape</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drape, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>clean vector clipart of draw, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>drift</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drift, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drink, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>driveway</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>clean vector clipart of driveway, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>droop</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>clean vector clipart of droop, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>droplet</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>clean vector clipart of droplet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>drought</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drought, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>drumstick</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>clean vector clipart of drumstick, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>dry</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dry, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>duckling</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>clean vector clipart of duckling, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>dumpling</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dumpling, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>dusk</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>clean vector clipart of dusk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>eardrum</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>clean vector clipart of eardrum, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Easter</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>clean vector clipart of Easter, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>eclair</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>clean vector clipart of eclair, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>eclipse</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>clean vector clipart of eclipse, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>eggplant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>clean vector clipart of eggplant, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>enclose</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>clean vector clipart of enclose, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>escape</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>clean vector clipart of escape, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>explain</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>clean vector clipart of explain, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>express</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>clean vector clipart of express, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>clean vector clipart of February, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fingerprint</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>clean vector clipart of fingerprint, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>firefly</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>clean vector clipart of firefly, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fireplace</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>clean vector clipart of fireplace, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>flask</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>clean vector clipart of flask, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>flavor</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>clean vector clipart of flavor, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>clean vector clipart of Florida, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>freckle</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>clean vector clipart of freckle, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>freedom</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>clean vector clipart of freedom, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>freight</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>clean vector clipart of freight, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>clean vector clipart of Friday, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>fries</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>clean vector clipart of fries, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>frisbee</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>clean vector clipart of frisbee, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>froglet</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>clean vector clipart of froglet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>clean vector clipart of front, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>frontflip</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>clean vector clipart of frontflip, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>frost</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>clean vector clipart of frost, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>fry</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>clean vector clipart of fry, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>gingerbread</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>clean vector clipart of gingerbread, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>glacier</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>clean vector clipart of glacier, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>glaze</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>clean vector clipart of glaze, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>glitter</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>clean vector clipart of glitter, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>gloom</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>clean vector clipart of gloom, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>gluten</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>clean vector clipart of gluten, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>gobbler</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>clean vector clipart of gobbler, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>goblet</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>clean vector clipart of goblet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>goblin</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>clean vector clipart of goblin, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>granola</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>clean vector clipart of granola, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>grapefruit</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>clean vector clipart of grapefruit, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>grasp</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>clean vector clipart of grasp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>grasslands</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>clean vector clipart of grasslands, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>grizzly</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>clean vector clipart of grizzly, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>gryffin</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>clean vector clipart of gryffin, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>halfling</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>clean vector clipart of halfling, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>hamster</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hamster, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>handrail</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>clean vector clipart of handrail, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>hang-glider</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hang-glider, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>headrest</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>clean vector clipart of headrest, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>hieroglyphics</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hieroglyphics, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>high school</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>clean vector clipart of high school, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>horsefly</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>clean vector clipart of horsefly, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hospital, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>hungry</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hungry, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>husk</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>clean vector clipart of husk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>husky</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>clean vector clipart of husky, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>hydrant</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hydrant, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>hydrate</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hydrate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>clean vector clipart of hydrogen, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ice cream</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>clean vector clipart of ice cream, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>iceskate</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>clean vector clipart of iceskate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>impress</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>clean vector clipart of impress, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>imprint</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>clean vector clipart of imprint, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>improve</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>clean vector clipart of improve, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>increase</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>clean vector clipart of increase, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>inflate</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>clean vector clipart of inflate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ingredient</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>clean vector clipart of ingredient, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ingrown</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>clean vector clipart of ingrown, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>jackfruit</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>clean vector clipart of jackfruit, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>jailbreak</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>clean vector clipart of jailbreak, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>jester</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>clean vector clipart of jester, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>jostle</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>clean vector clipart of jostle, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>journalism</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>clean vector clipart of journalism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>juggling</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>clean vector clipart of juggling, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>jumprope</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>clean vector clipart of jumprope, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>kiosk</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>clean vector clipart of kiosk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>lacrosse</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>clean vector clipart of lacrosse, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>clean vector clipart of library, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>lisp</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>clean vector clipart of lisp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>clean vector clipart of list, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>locksmith</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>clean vector clipart of locksmith, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>loosely</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>clean vector clipart of loosely, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>macrame</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>clean vector clipart of macrame, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>magnetism</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>clean vector clipart of magnetism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>mandrill</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mandrill, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>mascot</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mascot, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>mask</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mask, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>metabolism</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>clean vector clipart of metabolism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>microphone</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>clean vector clipart of microphone, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>microscope</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>clean vector clipart of microscope, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>clean vector clipart of microwave, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>migrate</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>clean vector clipart of migrate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>migration</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>clean vector clipart of migration, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>misleading</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>clean vector clipart of misleading, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mismatch, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>clean vector clipart of missile, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>mister</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mister, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>mollusc</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mollusc, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>mosque</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mosque, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>mosquito</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mosquito, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>mudflap</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mudflap, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>muesli</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>clean vector clipart of muesli, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>multiply</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>clean vector clipart of multiply, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>musk</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>clean vector clipart of musk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>muskrat</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>clean vector clipart of muskrat, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>muslin</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>clean vector clipart of muslin, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>mussel</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mussel, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>must</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>clean vector clipart of must, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>mustache</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>clean vector clipart of mustache, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>necklace</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>clean vector clipart of necklace, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>newspaper</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>clean vector clipart of newspaper, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>nucleus</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>clean vector clipart of nucleus, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>obelisk</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>clean vector clipart of obelisk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>oblong</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>clean vector clipart of oblong, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>off ramp</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>clean vector clipart of off ramp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>clean vector clipart of organism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>osprey</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>clean vector clipart of osprey, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>outsmart</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>clean vector clipart of outsmart, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>parcel</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>clean vector clipart of parcel, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>parsley</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>clean vector clipart of parsley, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>passionfruit</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>clean vector clipart of passionfruit, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>passport</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>clean vector clipart of passport, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>pedigree</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>clean vector clipart of pedigree, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>pessimism</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>clean vector clipart of pessimism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>petroglyph</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>clean vector clipart of petroglyph, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>photograph</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>clean vector clipart of photograph, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>photographer</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>clean vector clipart of photographer, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>pilgrim</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>clean vector clipart of pilgrim, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>placemat</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>clean vector clipart of placemat, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>plaque</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plaque, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>plasma</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plasma, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>plaster</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plaster, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plastic, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>plateau</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plateau, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>clean vector clipart of playground, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>plum</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plum, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>plumber</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plumber, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>plus</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plus, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>plywood</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>clean vector clipart of plywood, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>policeman</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>clean vector clipart of policeman, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>prank</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>clean vector clipart of prank, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>preschool</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>clean vector clipart of preschool, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>pretend</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>clean vector clipart of pretend, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>pretzel</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>clean vector clipart of pretzel, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>priceless</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>clean vector clipart of priceless, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>prism</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>clean vector clipart of prism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>program</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>clean vector clipart of program, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>clean vector clipart of progress, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>proud</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>clean vector clipart of proud, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>pueblo</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>clean vector clipart of pueblo, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>rasp</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>clean vector clipart of rasp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>reflect</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>clean vector clipart of reflect, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>reflex</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>clean vector clipart of reflex, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>refresh</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>clean vector clipart of refresh, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>respect</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>clean vector clipart of respect, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>respond</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>clean vector clipart of respond, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>clean vector clipart of risky, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>rust</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>clean vector clipart of rust, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>rusty</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>clean vector clipart of rusty, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>sacred</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sacred, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>saffron</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>clean vector clipart of saffron, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>salesman</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>clean vector clipart of salesman, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>sampler</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sampler, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>sapling</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sapling, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>sassafras</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sassafras, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>scales</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>clean vector clipart of scales, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>scarecrow</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>clean vector clipart of scarecrow, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>scone</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>clean vector clipart of scone, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>screwdriver</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>clean vector clipart of screwdriver, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>secret</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>clean vector clipart of secret, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>secretary</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>clean vector clipart of secretary, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>seismic</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>clean vector clipart of seismic, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>skillet</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>clean vector clipart of skillet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>clean vector clipart of skin, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>skirt</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>clean vector clipart of skirt, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>skull</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>clean vector clipart of skull, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>skunk</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>clean vector clipart of skunk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>slanted</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>clean vector clipart of slanted, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>sleigh</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sleigh, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>sloppy</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sloppy, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>clean vector clipart of slug, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>smelt</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smelt, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>smirk</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smirk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>smog</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smog, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>smokestack</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smokestack, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>smorgasbord</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smorgasbord, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>smudge</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smudge, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>smuggle</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>clean vector clipart of smuggle, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>sneaker</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sneaker, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>snorkel</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>clean vector clipart of snorkel, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>snowdrift</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>clean vector clipart of snowdrift, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>snowdrop</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>clean vector clipart of snowdrop, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>snowflake</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>clean vector clipart of snowflake, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>snowglobe</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>clean vector clipart of snowglobe, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>sombrero</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sombrero, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>spa</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>clean vector clipart of spa, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>spaceship</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>clean vector clipart of spaceship, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>spasm</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>clean vector clipart of spasm, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>spinach</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>clean vector clipart of spinach, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sports, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>sprain</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sprain, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>sprinkles</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sprinkles, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sprite, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>spurs</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>clean vector clipart of spurs, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stairs, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>stapler</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stapler, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>stars</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stars, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>stash</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stash, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>clean vector clipart of steam, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>stem</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stem, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>stool</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stool, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>stork</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stork, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>storm</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>clean vector clipart of storm, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>stump</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>clean vector clipart of stump, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>suffragette</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>clean vector clipart of suffragette, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>sunflower</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sunflower, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>sunglasses</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sunglasses, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>sunspot</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>clean vector clipart of sunspot, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>superglue</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>clean vector clipart of superglue, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>surprise</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>clean vector clipart of surprise, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>clean vector clipart of suspect, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>suspenders</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>clean vector clipart of suspenders, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>swaddle</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>clean vector clipart of swaddle, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>swamp</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>clean vector clipart of swamp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>swap</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>clean vector clipart of swap, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>swine</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>clean vector clipart of swine, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>swivel</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>clean vector clipart of swivel, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>tablet</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>clean vector clipart of tablet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>clean vector clipart of task, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>teaspoon</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>clean vector clipart of teaspoon, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>telegram</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>clean vector clipart of telegram, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>telescope</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>clean vector clipart of telescope, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>thirsty</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>clean vector clipart of thirsty, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>toaster</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>clean vector clipart of toaster, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>tourism</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>clean vector clipart of tourism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>translator</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>clean vector clipart of translator, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>triplet</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>clean vector clipart of triplet, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>clean vector clipart of trust, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>tusk</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>clean vector clipart of tusk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ugly</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>clean vector clipart of ugly, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>umbrella</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>clean vector clipart of umbrella, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>underground</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>clean vector clipart of underground, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>useless</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>clean vector clipart of useless, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>vandalism</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>clean vector clipart of vandalism, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>vibrate</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>clean vector clipart of vibrate, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>voiceless</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>clean vector clipart of voiceless, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>wasp</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>clean vector clipart of wasp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>clean vector clipart of West, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>whisk</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>clean vector clipart of whisk, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>whiskers</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>clean vector clipart of whiskers, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>whistling</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>clean vector clipart of whistling, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>wisp</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>clean vector clipart of wisp, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>wrist</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>clean vector clipart of wrist, centered, isolated, plain white background, minimal style, bold outline, no text, square composition</t>
         </is>
       </c>
     </row>
